--- a/config/saldos.example.xlsx
+++ b/config/saldos.example.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Saldo Diário" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Vencimentos RF" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,4 +485,364 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data de Atualização</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Código do Cliente</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Conta BTG</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Emissor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Quantidade</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Valor Custo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Indexador</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Taxa Compra</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Data Compra</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Vencimento</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Liquidez</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Visualização Cliente</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Valor Bruto - Curva Cliente</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>IR - Curva Cliente</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>IOF - Curva Cliente</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Valor Líquido - Curva Cliente</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Valor Bruto - Curva Mercado</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>IR - Curva Mercado</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>IOF - Curva Mercado</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ABC_XY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>001111111</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BANCO ABC DE INVESTIMENTO S.A.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDB-CDB1234AB1D</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>110% CDI</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>110</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>45545</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Vencimento</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Precificação na Curva Cliente</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>112500</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>104000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DEF_ZW</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>002222222</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MIDWAY S.A.- CREDITO FINANCIAMENTO E INVESTIMENTO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LCI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>LCI-24J0099887</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>95% CDI</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>95</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Liquidez Diaria</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Precificação na Curva Mercado</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>53200</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>53200</v>
+      </c>
+      <c r="S3" t="n">
+        <v>53200</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ABC_XY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>003333333</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CRI-22J0055443</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100% IPCA</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>44701</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>46397</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Precificação na Curva Cliente</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>28900</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>28900</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/config/saldos.example.xlsx
+++ b/config/saldos.example.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Saldo Diário" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Vencimentos RF" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,364 +484,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:V4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Data de Atualização</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Código do Cliente</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Conta BTG</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Emissor</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Quantidade</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Valor Custo</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Indexador</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Taxa Compra</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Data Compra</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Vencimento</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Liquidez</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Visualização Cliente</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Valor Bruto - Curva Cliente</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>IR - Curva Cliente</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>IOF - Curva Cliente</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Valor Líquido - Curva Cliente</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Valor Bruto - Curva Mercado</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>IR - Curva Mercado</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>IOF - Curva Mercado</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ABC_XY</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>001111111</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BANCO ABC DE INVESTIMENTO S.A.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CDB</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CDB-CDB1234AB1D</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>110% CDI</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>110</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>45545</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Vencimento</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Precificação na Curva Cliente</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>112500</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8500</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>104000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DEF_ZW</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>002222222</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MIDWAY S.A.- CREDITO FINANCIAMENTO E INVESTIMENTO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LCI</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>LCI-24J0099887</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>95% CDI</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>95</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>45353</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Liquidez Diaria</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Precificação na Curva Mercado</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>53200</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>53200</v>
-      </c>
-      <c r="S3" t="n">
-        <v>53200</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ABC_XY</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>003333333</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CAIXA ECONOMICA FEDERAL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CRI</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CRI-22J0055443</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100% IPCA</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>44701</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>46397</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Precificação na Curva Cliente</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>28900</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>28900</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1003</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/config/saldos.example.xlsx
+++ b/config/saldos.example.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Saldo Diário" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Export" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,23 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Conta do BTG</t>
+          <t>Conta BTG</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código do Cliente</t>
+          <t>Nome do Cliente</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
           <t>Saldo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Responsável</t>
         </is>
       </c>
     </row>
@@ -450,6 +452,11 @@
       <c r="C2" t="n">
         <v>12345.67</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -465,6 +472,11 @@
       <c r="C3" t="n">
         <v>890.1</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -474,11 +486,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ABC_XY</t>
+          <t>GHI_QR</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>250</v>
+        <v>-250</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Beltrano Souza</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/saldos.example.xlsx
+++ b/config/saldos.example.xlsx
@@ -413,8 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -441,16 +447,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>001111111</t>
+          <t>000100001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABC_XY</t>
+          <t>CLI_100001</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12345.67</v>
+        <v>-5225.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -461,16 +467,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002222222</t>
+          <t>000100002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEF_ZW</t>
+          <t>CLI_100002</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>890.1</v>
+        <v>106.77</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -481,20 +487,480 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>003333333</t>
+          <t>000100003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GHI_QR</t>
+          <t>CLI_100003</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-250</v>
+        <v>0.36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>000100004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CLI_100004</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>000100005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLI_100005</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>000100006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CLI_100006</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>000100007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CLI_100007</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>000100008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CLI_100008</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>000100009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CLI_100009</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>000100010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CLI_100010</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>7870.74</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>000100011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CLI_100011</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>23810.86</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>000100012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CLI_100012</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>000100013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CLI_100013</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>000100014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CLI_100014</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1287.81</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>000100015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CLI_100015</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>462.72</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>000100016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CLI_100016</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>000100017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CLI_100017</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>577.89</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>000100018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLI_100018</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>559.3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>000100019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CLI_100019</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Beltrano Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>000100020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CLI_100020</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Beltrano Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>000100021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CLI_100021</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1003.98</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Beltrano Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>000100022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CLI_100022</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6285.02</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Beltrano Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>000100023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CLI_100023</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3037.88</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Beltrano Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>000100024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CLI_100024</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ciclano Nunes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>000100025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CLI_100025</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-492.32</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ciclano Nunes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>000100026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CLI_100026</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ciclano Nunes</t>
         </is>
       </c>
     </row>

--- a/config/saldos.example.xlsx
+++ b/config/saldos.example.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Export" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Investimentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Banking" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -967,4 +968,126 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Conta BTG</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nome do Cliente</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Saldo Banking (R$)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>000100001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CLI_100001</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>850</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>000100004</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CLI_100004</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>000100011</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CLI_100011</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12500.4</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fulano Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>000100020</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CLI_100020</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>220.15</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Beltrano Souza</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>